--- a/Coimbatore-November-2025.xlsx
+++ b/Coimbatore-November-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Coimbatore</t>
   </si>
   <si>
@@ -109,19 +112,16 @@
     <t>TN09DF3647</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Etios</t>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>ETIOS</t>
   </si>
   <si>
     <t>29/01/2020</t>
   </si>
   <si>
     <t>24/05/2019</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -479,10 +479,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,28 +561,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>270</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2">
         <v>85157</v>
@@ -642,27 +645,27 @@
         <v>62.31</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>271</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3">
         <v>235485</v>
@@ -722,24 +725,24 @@
         <v>57.3</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>272</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
         <v>35</v>
